--- a/old_vs_new_records.xlsx
+++ b/old_vs_new_records.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git Projects\Mora-Bird-Diversity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D58BB59-D447-4D7A-B0AB-742FF417AC03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F70BFD65-13D0-46C9-810A-900056508A2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="15324" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -535,6 +535,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>LITTLE RINGED PLOVER-</t>
     </r>
@@ -553,6 +554,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>LITTLE RINGED PLOVER-</t>
     </r>
@@ -571,6 +573,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>KENTISH PLOVER-</t>
     </r>
@@ -589,6 +592,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>KENTISH PLOVER-</t>
     </r>
@@ -1123,6 +1127,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>BARN SWALLOW-</t>
     </r>
@@ -1141,6 +1146,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>BARN SWALLOW-</t>
     </r>
@@ -1159,6 +1165,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>RED RUMPED SWALLOW-</t>
     </r>
@@ -1177,6 +1184,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>RED RUMPED SWALLOW-</t>
     </r>
@@ -1201,6 +1209,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>WESTERN YELLOW WAGTAIL-</t>
     </r>
@@ -1219,6 +1228,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>WESTERN YELLOW WAGTAIL-</t>
     </r>
@@ -1237,6 +1247,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>WESTERN YELLOW WAGTAIL-</t>
     </r>
@@ -1255,6 +1266,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>EASTERN YELLOW WAGTAIL-</t>
     </r>
@@ -1663,6 +1675,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>EUROPEAN GOLDEN ORIOLE-</t>
     </r>
@@ -1681,6 +1694,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>INDIAN GOLDEN ORIOLE-</t>
     </r>
@@ -1769,15 +1783,18 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -1907,7 +1924,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1922,6 +1939,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1932,7 +1950,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4624,9 +4642,13 @@
         <v>255</v>
       </c>
       <c r="B254" s="2"/>
-      <c r="C254" s="3"/>
+      <c r="C254" s="3">
+        <v>1</v>
+      </c>
       <c r="D254" s="1"/>
-      <c r="E254" s="1"/>
+      <c r="E254" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="255" spans="1:5" ht="15.75" customHeight="1">
       <c r="A255" s="1" t="s">
@@ -4675,10 +4697,10 @@
       <c r="B259" s="2">
         <v>1</v>
       </c>
-      <c r="C259" s="3"/>
-      <c r="D259" s="7">
-        <v>1</v>
-      </c>
+      <c r="C259" s="3">
+        <v>1</v>
+      </c>
+      <c r="D259" s="19"/>
       <c r="E259" s="1"/>
     </row>
     <row r="260" spans="1:5" ht="15.75" customHeight="1">
@@ -4735,9 +4757,13 @@
         <v>266</v>
       </c>
       <c r="B265" s="2"/>
-      <c r="C265" s="3"/>
+      <c r="C265" s="3">
+        <v>1</v>
+      </c>
       <c r="D265" s="1"/>
-      <c r="E265" s="1"/>
+      <c r="E265" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="266" spans="1:5" ht="15.75" customHeight="1">
       <c r="A266" s="1" t="s">
@@ -5308,9 +5334,13 @@
         <v>323</v>
       </c>
       <c r="B322" s="2"/>
-      <c r="C322" s="3"/>
+      <c r="C322" s="3">
+        <v>1</v>
+      </c>
       <c r="D322" s="1"/>
-      <c r="E322" s="1"/>
+      <c r="E322" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="323" spans="1:5" ht="15.75" customHeight="1">
       <c r="A323" s="1" t="s">
@@ -5368,10 +5398,10 @@
       <c r="B328" s="2">
         <v>1</v>
       </c>
-      <c r="C328" s="3"/>
-      <c r="D328" s="7">
-        <v>1</v>
-      </c>
+      <c r="C328" s="3">
+        <v>1</v>
+      </c>
+      <c r="D328" s="19"/>
       <c r="E328" s="1"/>
     </row>
     <row r="329" spans="1:5" ht="15.75" customHeight="1">
@@ -5490,11 +5520,11 @@
       <c r="A341" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B341" s="14">
-        <v>1</v>
-      </c>
-      <c r="C341" s="16"/>
-      <c r="D341" s="17">
+      <c r="B341" s="15">
+        <v>1</v>
+      </c>
+      <c r="C341" s="17"/>
+      <c r="D341" s="18">
         <v>1</v>
       </c>
       <c r="E341" s="1"/>
@@ -5503,9 +5533,9 @@
       <c r="A342" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B342" s="15"/>
-      <c r="C342" s="15"/>
-      <c r="D342" s="15"/>
+      <c r="B342" s="16"/>
+      <c r="C342" s="16"/>
+      <c r="D342" s="16"/>
       <c r="E342" s="1"/>
     </row>
     <row r="343" spans="1:5" ht="15.75" customHeight="1">
@@ -5829,7 +5859,7 @@
       <c r="C374" s="3">
         <v>1</v>
       </c>
-      <c r="D374" s="18"/>
+      <c r="D374" s="14"/>
       <c r="E374" s="1"/>
     </row>
     <row r="375" spans="1:5" ht="15.75" customHeight="1">
@@ -5984,9 +6014,13 @@
         <v>391</v>
       </c>
       <c r="B390" s="2"/>
-      <c r="C390" s="3"/>
+      <c r="C390" s="3">
+        <v>1</v>
+      </c>
       <c r="D390" s="1"/>
-      <c r="E390" s="1"/>
+      <c r="E390" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="391" spans="1:5" ht="15.75" customHeight="1">
       <c r="A391" s="1" t="s">
@@ -6290,10 +6324,10 @@
       <c r="B422" s="2">
         <v>1</v>
       </c>
-      <c r="C422" s="3"/>
-      <c r="D422" s="7">
-        <v>1</v>
-      </c>
+      <c r="C422" s="3">
+        <v>1</v>
+      </c>
+      <c r="D422" s="19"/>
       <c r="E422" s="1"/>
     </row>
     <row r="423" spans="1:5" ht="15.75" customHeight="1">
@@ -6415,10 +6449,10 @@
       <c r="B435" s="2">
         <v>1</v>
       </c>
-      <c r="C435" s="3"/>
-      <c r="D435" s="7">
-        <v>1</v>
-      </c>
+      <c r="C435" s="3">
+        <v>1</v>
+      </c>
+      <c r="D435" s="19"/>
       <c r="E435" s="1"/>
     </row>
     <row r="436" spans="1:5" ht="15.75" customHeight="1">
@@ -6573,9 +6607,13 @@
         <v>452</v>
       </c>
       <c r="B451" s="2"/>
-      <c r="C451" s="3"/>
+      <c r="C451" s="3">
+        <v>1</v>
+      </c>
       <c r="D451" s="1"/>
-      <c r="E451" s="1"/>
+      <c r="E451" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="452" spans="1:5" ht="15.75" customHeight="1">
       <c r="A452" s="1" t="s">
@@ -7074,15 +7112,15 @@
       </c>
       <c r="C501" s="3">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="D501" s="1">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E501" s="1">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="502" spans="1:5" ht="15.75" customHeight="1">
